--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -62886,6 +62886,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.0297999996691942</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.0297999996691942</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.0297999996691942</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.0297999996691942</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>602738</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.0283000003546476</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.0267999991774559</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.0273000001907349</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.0280000008642673</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>782004</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.0280000008642673</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.0260000005364418</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.0280000008642673</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.0264999996870756</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>445315</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.0278999991714954</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.0258000008761883</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.0278999991714954</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.0260000005364418</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>43257</v>
+        <v>55001</v>
       </c>
       <c r="C2715" t="n">
-        <v>0.0307000000029802</v>
+        <v>0.029899999499321</v>
       </c>
       <c r="D2715" t="n">
-        <v>0.028999999165535</v>
+        <v>0.029899999499321</v>
       </c>
       <c r="E2715" t="n">
-        <v>0.0295000001788139</v>
+        <v>0.029899999499321</v>
       </c>
       <c r="F2715" t="n">
-        <v>0.0291000008583069</v>
+        <v>0.029899999499321</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>274351</v>
+        <v>43257</v>
       </c>
       <c r="C2716" t="n">
-        <v>0.0304000005125999</v>
+        <v>0.0307000000029802</v>
       </c>
       <c r="D2716" t="n">
-        <v>0.0295000001788139</v>
+        <v>0.028999999165535</v>
       </c>
       <c r="E2716" t="n">
         <v>0.0295000001788139</v>
       </c>
       <c r="F2716" t="n">
-        <v>0.0299999993294477</v>
+        <v>0.0291000008583069</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>11690</v>
+        <v>274351</v>
       </c>
       <c r="C2717" t="n">
-        <v>0.0306000001728535</v>
+        <v>0.0304000005125999</v>
       </c>
       <c r="D2717" t="n">
-        <v>0.0293000005185604</v>
+        <v>0.0295000001788139</v>
       </c>
       <c r="E2717" t="n">
-        <v>0.0304000005125999</v>
+        <v>0.0295000001788139</v>
       </c>
       <c r="F2717" t="n">
-        <v>0.0297999996691942</v>
+        <v>0.0299999993294477</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,19 +62865,19 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>110675</v>
+        <v>11690</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.0297999996691942</v>
+        <v>0.0306000001728535</v>
       </c>
       <c r="D2718" t="n">
-        <v>0.0287999995052814</v>
+        <v>0.0293000005185604</v>
       </c>
       <c r="E2718" t="n">
-        <v>0.028999999165535</v>
+        <v>0.0304000005125999</v>
       </c>
       <c r="F2718" t="n">
         <v>0.0297999996691942</v>
@@ -62888,19 +62888,19 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>0</v>
+        <v>110675</v>
       </c>
       <c r="C2719" t="n">
         <v>0.0297999996691942</v>
       </c>
       <c r="D2719" t="n">
-        <v>0.0297999996691942</v>
+        <v>0.0287999995052814</v>
       </c>
       <c r="E2719" t="n">
-        <v>0.0297999996691942</v>
+        <v>0.028999999165535</v>
       </c>
       <c r="F2719" t="n">
         <v>0.0297999996691942</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>602738</v>
+        <v>0</v>
       </c>
       <c r="C2720" t="n">
-        <v>0.0283000003546476</v>
+        <v>0.0297999996691942</v>
       </c>
       <c r="D2720" t="n">
-        <v>0.0267999991774559</v>
+        <v>0.0297999996691942</v>
       </c>
       <c r="E2720" t="n">
-        <v>0.0273000001907349</v>
+        <v>0.0297999996691942</v>
       </c>
       <c r="F2720" t="n">
-        <v>0.0280000008642673</v>
+        <v>0.0297999996691942</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>782004</v>
+        <v>602738</v>
       </c>
       <c r="C2721" t="n">
+        <v>0.0283000003546476</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.0267999991774559</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.0273000001907349</v>
+      </c>
+      <c r="F2721" t="n">
         <v>0.0280000008642673</v>
-      </c>
-      <c r="D2721" t="n">
-        <v>0.0260000005364418</v>
-      </c>
-      <c r="E2721" t="n">
-        <v>0.0280000008642673</v>
-      </c>
-      <c r="F2721" t="n">
-        <v>0.0264999996870756</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>445315</v>
+        <v>782004</v>
       </c>
       <c r="C2722" t="n">
-        <v>0.0278999991714954</v>
+        <v>0.0280000008642673</v>
       </c>
       <c r="D2722" t="n">
-        <v>0.0258000008761883</v>
+        <v>0.0260000005364418</v>
       </c>
       <c r="E2722" t="n">
-        <v>0.0278999991714954</v>
+        <v>0.0280000008642673</v>
       </c>
       <c r="F2722" t="n">
-        <v>0.0260000005364418</v>
+        <v>0.0264999996870756</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>1352687</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>0.0274999998509884</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>0.0241999998688698</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>0.0255999993532896</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>0.0269000008702278</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -447,7 +447,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>5.74289798736572</v>
+        <v>5.74289751052856</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G9" t="n">
-        <v>5.71334600448608</v>
+        <v>5.71334648132324</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G15" t="n">
-        <v>4.90953731536865</v>
+        <v>4.90953779220581</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G16" t="n">
-        <v>5.16171264648438</v>
+        <v>5.16171216964722</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>5.21096515655518</v>
+        <v>5.21096563339233</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G21" t="n">
-        <v>5.17648887634277</v>
+        <v>5.17648839950562</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>5.21096515655518</v>
+        <v>5.21096563339233</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G28" t="n">
-        <v>3.58561730384827</v>
+        <v>3.58561706542969</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G30" t="n">
-        <v>3.79050946235657</v>
+        <v>3.79050970077515</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G31" t="n">
-        <v>3.90280628204346</v>
+        <v>3.90280604362488</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>4.62978029251099</v>
+        <v>4.62977981567383</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G35" t="n">
-        <v>4.57658720016479</v>
+        <v>4.57658672332764</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G38" t="n">
-        <v>5.51140880584717</v>
+        <v>5.51140832901001</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>5.29962110519409</v>
+        <v>5.29962062835693</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>5.29962110519409</v>
+        <v>5.29962062835693</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G49" t="n">
-        <v>4.9991774559021</v>
+        <v>4.99917793273926</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G52" t="n">
-        <v>4.95485019683838</v>
+        <v>4.95485067367554</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G59" t="n">
-        <v>4.66918230056763</v>
+        <v>4.66918277740479</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G61" t="n">
-        <v>4.34608316421509</v>
+        <v>4.34608364105225</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G63" t="n">
-        <v>4.4583797454834</v>
+        <v>4.45838022232056</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G64" t="n">
-        <v>4.36381387710571</v>
+        <v>4.36381435394287</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>4.23575639724731</v>
+        <v>4.23575687408447</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G67" t="n">
-        <v>4.0742073059082</v>
+        <v>4.07420682907104</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.05844593048096</v>
+        <v>4.0584454536438</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.08799743652344</v>
+        <v>4.0879979133606</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>4.0485954284668</v>
+        <v>4.04859495162964</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G76" t="n">
-        <v>3.99343180656433</v>
+        <v>3.99343156814575</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G78" t="n">
-        <v>3.94220852851868</v>
+        <v>3.94220876693726</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G86" t="n">
-        <v>3.93629860877991</v>
+        <v>3.93629837036133</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G87" t="n">
-        <v>3.94417881965637</v>
+        <v>3.94417905807495</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95599937438965</v>
+        <v>3.95599913597107</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G92" t="n">
-        <v>3.92250776290894</v>
+        <v>3.92250752449036</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G96" t="n">
-        <v>3.93629860877991</v>
+        <v>3.93629837036133</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G98" t="n">
-        <v>3.9106867313385</v>
+        <v>3.91068696975708</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>0.025000000372529</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>1074890</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>0.0253999996930361</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>0.0243999995291233</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>0.0253999996930361</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>0.0243999995291233</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>0.0243999995291233</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -71251,6 +71251,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>204569</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>0.0248000007122755</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>0.023199999704957</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>0.023199999704957</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>0.0238000005483627</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>0.0238000005483627</v>
+      </c>
+      <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -447,7 +447,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>5.74289751052856</v>
+        <v>5.74289798736572</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G9" t="n">
-        <v>5.71334648132324</v>
+        <v>5.71334600448608</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G15" t="n">
-        <v>4.90953779220581</v>
+        <v>4.90953731536865</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G16" t="n">
-        <v>5.16171216964722</v>
+        <v>5.16171264648438</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>5.21096563339233</v>
+        <v>5.21096515655518</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G21" t="n">
-        <v>5.17648839950562</v>
+        <v>5.17648887634277</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>5.21096563339233</v>
+        <v>5.21096515655518</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G28" t="n">
-        <v>3.58561706542969</v>
+        <v>3.58561730384827</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G30" t="n">
-        <v>3.79050970077515</v>
+        <v>3.79050946235657</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G31" t="n">
-        <v>3.90280604362488</v>
+        <v>3.90280628204346</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>4.62977981567383</v>
+        <v>4.62978029251099</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G35" t="n">
-        <v>4.57658672332764</v>
+        <v>4.57658720016479</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G38" t="n">
-        <v>5.51140832901001</v>
+        <v>5.51140880584717</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>5.29962062835693</v>
+        <v>5.29962110519409</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>5.29962062835693</v>
+        <v>5.29962110519409</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G49" t="n">
-        <v>4.99917793273926</v>
+        <v>4.9991774559021</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G52" t="n">
-        <v>4.95485067367554</v>
+        <v>4.95485019683838</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G59" t="n">
-        <v>4.66918277740479</v>
+        <v>4.66918230056763</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G61" t="n">
-        <v>4.34608364105225</v>
+        <v>4.34608316421509</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G63" t="n">
-        <v>4.45838022232056</v>
+        <v>4.4583797454834</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G64" t="n">
-        <v>4.36381435394287</v>
+        <v>4.36381387710571</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>4.23575687408447</v>
+        <v>4.23575639724731</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G67" t="n">
-        <v>4.07420682907104</v>
+        <v>4.0742073059082</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.0584454536438</v>
+        <v>4.05844593048096</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.0879979133606</v>
+        <v>4.08799743652344</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>4.04859495162964</v>
+        <v>4.0485954284668</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G76" t="n">
-        <v>3.99343156814575</v>
+        <v>3.99343180656433</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G78" t="n">
-        <v>3.94220876693726</v>
+        <v>3.94220852851868</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G86" t="n">
-        <v>3.93629837036133</v>
+        <v>3.93629860877991</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G87" t="n">
-        <v>3.94417905807495</v>
+        <v>3.94417881965637</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95599913597107</v>
+        <v>3.95599937438965</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G92" t="n">
-        <v>3.92250752449036</v>
+        <v>3.92250776290894</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G96" t="n">
-        <v>3.93629837036133</v>
+        <v>3.93629860877991</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G98" t="n">
-        <v>3.91068696975708</v>
+        <v>3.9106867313385</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>0.0238000005483627</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>354118</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>0.0233999993652105</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -71303,6 +71303,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>5298698</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>0.0221999995410442</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>0.0219000000506639</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>0.0219000000506639</v>
+      </c>
+      <c r="H2729" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -71381,6 +71381,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>156883</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>0.0211999993771315</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>0.0203000009059906</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>0.0210999995470047</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>0.0206000003963709</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>0.0206000003963709</v>
+      </c>
+      <c r="H2732" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>0.0267999991774559</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>0.0261000003665686</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>1319410</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.0264999996870756</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.0243999995291233</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.0260000005364418</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>0.0260000005364418</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.0263999998569489</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>913307</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.0265999995172024</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.0245999991893768</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.0265999995172024</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>0.0265999995172024</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.0255999993532896</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>310571</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.025900000706315</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.0240000002086163</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.0255999993532896</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>0.0255999993532896</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>0.0240000002086163</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>79809</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>0.0253999996930361</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>0.0243999995291233</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>0.025000000372529</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>624120</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.024100000038743</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.02280000038445</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.0240000002086163</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -447,7 +447,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>5.74289751052856</v>
+        <v>5.74289798736572</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G9" t="n">
-        <v>5.71334648132324</v>
+        <v>5.71334600448608</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G15" t="n">
-        <v>4.90953779220581</v>
+        <v>4.90953731536865</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G16" t="n">
-        <v>5.16171216964722</v>
+        <v>5.16171264648438</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>5.21096563339233</v>
+        <v>5.21096515655518</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G21" t="n">
-        <v>5.17648839950562</v>
+        <v>5.17648887634277</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>5.21096563339233</v>
+        <v>5.21096515655518</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G28" t="n">
-        <v>3.58561706542969</v>
+        <v>3.58561730384827</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G30" t="n">
-        <v>3.79050970077515</v>
+        <v>3.79050946235657</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G31" t="n">
-        <v>3.90280604362488</v>
+        <v>3.90280628204346</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>4.62977981567383</v>
+        <v>4.62978029251099</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G35" t="n">
-        <v>4.57658672332764</v>
+        <v>4.57658720016479</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G38" t="n">
-        <v>5.51140832901001</v>
+        <v>5.51140880584717</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>5.29962062835693</v>
+        <v>5.29962110519409</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>5.29962062835693</v>
+        <v>5.29962110519409</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G49" t="n">
-        <v>4.99917793273926</v>
+        <v>4.9991774559021</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G52" t="n">
-        <v>4.95485067367554</v>
+        <v>4.95485019683838</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G59" t="n">
-        <v>4.66918277740479</v>
+        <v>4.66918230056763</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G61" t="n">
-        <v>4.34608364105225</v>
+        <v>4.34608316421509</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G63" t="n">
-        <v>4.45838022232056</v>
+        <v>4.4583797454834</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G64" t="n">
-        <v>4.36381435394287</v>
+        <v>4.36381387710571</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>4.23575687408447</v>
+        <v>4.23575639724731</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G67" t="n">
-        <v>4.07420682907104</v>
+        <v>4.0742073059082</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.0584454536438</v>
+        <v>4.05844593048096</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.0879979133606</v>
+        <v>4.08799743652344</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>4.04859495162964</v>
+        <v>4.0485954284668</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G76" t="n">
-        <v>3.99343156814575</v>
+        <v>3.99343180656433</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G78" t="n">
-        <v>3.94220876693726</v>
+        <v>3.94220852851868</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G86" t="n">
-        <v>3.93629837036133</v>
+        <v>3.93629860877991</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G87" t="n">
-        <v>3.94417905807495</v>
+        <v>3.94417881965637</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95599913597107</v>
+        <v>3.95599937438965</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G92" t="n">
-        <v>3.92250752449036</v>
+        <v>3.92250776290894</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G96" t="n">
-        <v>3.93629837036133</v>
+        <v>3.93629860877991</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G98" t="n">
-        <v>3.91068696975708</v>
+        <v>3.9106867313385</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>0.0230000000447035</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>10001</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>0.023199999704957</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>0.023199999704957</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>0.023199999704957</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -71678,7 +71678,7 @@
         <v>0.023199999704957</v>
       </c>
       <c r="D2743" t="n">
-        <v>0.023199999704957</v>
+        <v>0.0230000000447035</v>
       </c>
       <c r="E2743" t="n">
         <v>0.023199999704957</v>
@@ -71690,6 +71690,32 @@
         <v>0.0230000000447035</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>388254</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>0.0219000000506639</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>0.0219000000506639</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -79954,6 +79954,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>0.0234999991953373</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>0.0216000005602837</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>0.0220999997109175</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>0.0220999997109175</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>84290</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.0210999995470047</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.0255999993532896</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.0210999995470047</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>0.0239000003784895</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>0.0239000003784895</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>1456377</v>
+      </c>
+      <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -456,7 +456,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>5.74289798736572</v>
+        <v>5.74289751052856</v>
       </c>
       <c r="H3" t="n">
         <v>209257</v>
@@ -630,7 +630,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G9" t="n">
-        <v>5.71334600448608</v>
+        <v>5.71334648132324</v>
       </c>
       <c r="H9" t="n">
         <v>226982</v>
@@ -804,7 +804,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G15" t="n">
-        <v>4.90953731536865</v>
+        <v>4.90953779220581</v>
       </c>
       <c r="H15" t="n">
         <v>908989</v>
@@ -833,7 +833,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G16" t="n">
-        <v>5.16171264648438</v>
+        <v>5.16171216964722</v>
       </c>
       <c r="H16" t="n">
         <v>470293</v>
@@ -949,7 +949,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>5.21096515655518</v>
+        <v>5.21096563339233</v>
       </c>
       <c r="H20" t="n">
         <v>126286</v>
@@ -978,7 +978,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G21" t="n">
-        <v>5.17648887634277</v>
+        <v>5.17648839950562</v>
       </c>
       <c r="H21" t="n">
         <v>124704</v>
@@ -1007,7 +1007,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>5.21096515655518</v>
+        <v>5.21096563339233</v>
       </c>
       <c r="H22" t="n">
         <v>196742</v>
@@ -1181,7 +1181,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G28" t="n">
-        <v>3.58561730384827</v>
+        <v>3.58561706542969</v>
       </c>
       <c r="H28" t="n">
         <v>598311</v>
@@ -1239,7 +1239,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G30" t="n">
-        <v>3.79050946235657</v>
+        <v>3.79050970077515</v>
       </c>
       <c r="H30" t="n">
         <v>438905</v>
@@ -1268,7 +1268,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G31" t="n">
-        <v>3.90280628204346</v>
+        <v>3.90280604362488</v>
       </c>
       <c r="H31" t="n">
         <v>361003</v>
@@ -1355,7 +1355,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>4.62978029251099</v>
+        <v>4.62977981567383</v>
       </c>
       <c r="H34" t="n">
         <v>445139</v>
@@ -1384,7 +1384,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G35" t="n">
-        <v>4.57658720016479</v>
+        <v>4.57658672332764</v>
       </c>
       <c r="H35" t="n">
         <v>660456</v>
@@ -1471,7 +1471,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G38" t="n">
-        <v>5.51140880584717</v>
+        <v>5.51140832901001</v>
       </c>
       <c r="H38" t="n">
         <v>972499</v>
@@ -1558,7 +1558,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>5.29962110519409</v>
+        <v>5.29962062835693</v>
       </c>
       <c r="H41" t="n">
         <v>390501</v>
@@ -1587,7 +1587,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>5.29962110519409</v>
+        <v>5.29962062835693</v>
       </c>
       <c r="H42" t="n">
         <v>506725</v>
@@ -1790,7 +1790,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G49" t="n">
-        <v>4.9991774559021</v>
+        <v>4.99917793273926</v>
       </c>
       <c r="H49" t="n">
         <v>389307</v>
@@ -1877,7 +1877,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G52" t="n">
-        <v>4.95485019683838</v>
+        <v>4.95485067367554</v>
       </c>
       <c r="H52" t="n">
         <v>406656</v>
@@ -2080,7 +2080,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G59" t="n">
-        <v>4.66918230056763</v>
+        <v>4.66918277740479</v>
       </c>
       <c r="H59" t="n">
         <v>322258</v>
@@ -2138,7 +2138,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G61" t="n">
-        <v>4.34608316421509</v>
+        <v>4.34608364105225</v>
       </c>
       <c r="H61" t="n">
         <v>512194</v>
@@ -2196,7 +2196,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G63" t="n">
-        <v>4.4583797454834</v>
+        <v>4.45838022232056</v>
       </c>
       <c r="H63" t="n">
         <v>651861</v>
@@ -2225,7 +2225,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G64" t="n">
-        <v>4.36381387710571</v>
+        <v>4.36381435394287</v>
       </c>
       <c r="H64" t="n">
         <v>521178</v>
@@ -2254,7 +2254,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>4.23575639724731</v>
+        <v>4.23575687408447</v>
       </c>
       <c r="H65" t="n">
         <v>607840</v>
@@ -2312,7 +2312,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G67" t="n">
-        <v>4.0742073059082</v>
+        <v>4.07420682907104</v>
       </c>
       <c r="H67" t="n">
         <v>347657</v>
@@ -2370,7 +2370,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.05844593048096</v>
+        <v>4.0584454536438</v>
       </c>
       <c r="H69" t="n">
         <v>275320</v>
@@ -2399,7 +2399,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.08799743652344</v>
+        <v>4.0879979133606</v>
       </c>
       <c r="H70" t="n">
         <v>183131</v>
@@ -2515,7 +2515,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>4.0485954284668</v>
+        <v>4.04859495162964</v>
       </c>
       <c r="H74" t="n">
         <v>139031</v>
@@ -2573,7 +2573,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G76" t="n">
-        <v>3.99343180656433</v>
+        <v>3.99343156814575</v>
       </c>
       <c r="H76" t="n">
         <v>239763</v>
@@ -2631,7 +2631,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G78" t="n">
-        <v>3.94220852851868</v>
+        <v>3.94220876693726</v>
       </c>
       <c r="H78" t="n">
         <v>199710</v>
@@ -2863,7 +2863,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G86" t="n">
-        <v>3.93629860877991</v>
+        <v>3.93629837036133</v>
       </c>
       <c r="H86" t="n">
         <v>139234</v>
@@ -2892,7 +2892,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G87" t="n">
-        <v>3.94417881965637</v>
+        <v>3.94417905807495</v>
       </c>
       <c r="H87" t="n">
         <v>95738</v>
@@ -3008,7 +3008,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95599937438965</v>
+        <v>3.95599913597107</v>
       </c>
       <c r="H91" t="n">
         <v>78796</v>
@@ -3037,7 +3037,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G92" t="n">
-        <v>3.92250776290894</v>
+        <v>3.92250752449036</v>
       </c>
       <c r="H92" t="n">
         <v>96082</v>
@@ -3153,7 +3153,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G96" t="n">
-        <v>3.93629860877991</v>
+        <v>3.93629837036133</v>
       </c>
       <c r="H96" t="n">
         <v>110034</v>
@@ -3211,7 +3211,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G98" t="n">
-        <v>3.9106867313385</v>
+        <v>3.91068696975708</v>
       </c>
       <c r="H98" t="n">
         <v>70667</v>
@@ -80009,6 +80009,35 @@
         <v>1456377</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>0.0239000003784895</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>0.0239000003784895</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>0.0226000007241964</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>0.0236000008881092</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>0.0236000008881092</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>721603</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -80041,6 +80041,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>0.0240000002086163</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>0.0240000002086163</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>0.0219999998807907</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>0.0216000005602837</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>0.0216000005602837</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>490569</v>
+      </c>
+      <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -80055,7 +80055,7 @@
         <v>0.0240000002086163</v>
       </c>
       <c r="E2748" t="n">
-        <v>0.0219999998807907</v>
+        <v>0.0216000005602837</v>
       </c>
       <c r="F2748" t="n">
         <v>0.0216000005602837</v>
@@ -80067,6 +80067,35 @@
         <v>490569</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>0.0219999998807907</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>0.0219999998807907</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>0.0204000007361174</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>0.0205000005662441</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>0.0205000005662441</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>173182</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -80099,6 +80099,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>0.0201999992132187</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>0.0206000003963709</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>1501903</v>
+      </c>
+      <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -80128,6 +80128,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>0.0201999992132187</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>177705</v>
+      </c>
+      <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -80157,6 +80157,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>0.0229000002145767</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>0.0199999995529652</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>0.0215000007301569</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>0.0215000007301569</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>1101641</v>
+      </c>
+      <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -456,7 +456,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>5.74289751052856</v>
+        <v>5.74289798736572</v>
       </c>
       <c r="H3" t="n">
         <v>209257</v>
@@ -630,7 +630,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G9" t="n">
-        <v>5.71334648132324</v>
+        <v>5.71334600448608</v>
       </c>
       <c r="H9" t="n">
         <v>226982</v>
@@ -804,7 +804,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G15" t="n">
-        <v>4.90953779220581</v>
+        <v>4.90953731536865</v>
       </c>
       <c r="H15" t="n">
         <v>908989</v>
@@ -833,7 +833,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G16" t="n">
-        <v>5.16171216964722</v>
+        <v>5.16171264648438</v>
       </c>
       <c r="H16" t="n">
         <v>470293</v>
@@ -949,7 +949,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>5.21096563339233</v>
+        <v>5.21096515655518</v>
       </c>
       <c r="H20" t="n">
         <v>126286</v>
@@ -978,7 +978,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G21" t="n">
-        <v>5.17648839950562</v>
+        <v>5.17648887634277</v>
       </c>
       <c r="H21" t="n">
         <v>124704</v>
@@ -1007,7 +1007,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>5.21096563339233</v>
+        <v>5.21096515655518</v>
       </c>
       <c r="H22" t="n">
         <v>196742</v>
@@ -1181,7 +1181,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G28" t="n">
-        <v>3.58561706542969</v>
+        <v>3.58561730384827</v>
       </c>
       <c r="H28" t="n">
         <v>598311</v>
@@ -1239,7 +1239,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G30" t="n">
-        <v>3.79050970077515</v>
+        <v>3.79050946235657</v>
       </c>
       <c r="H30" t="n">
         <v>438905</v>
@@ -1268,7 +1268,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G31" t="n">
-        <v>3.90280604362488</v>
+        <v>3.90280628204346</v>
       </c>
       <c r="H31" t="n">
         <v>361003</v>
@@ -1355,7 +1355,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>4.62977981567383</v>
+        <v>4.62978029251099</v>
       </c>
       <c r="H34" t="n">
         <v>445139</v>
@@ -1384,7 +1384,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G35" t="n">
-        <v>4.57658672332764</v>
+        <v>4.57658720016479</v>
       </c>
       <c r="H35" t="n">
         <v>660456</v>
@@ -1471,7 +1471,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G38" t="n">
-        <v>5.51140832901001</v>
+        <v>5.51140880584717</v>
       </c>
       <c r="H38" t="n">
         <v>972499</v>
@@ -1558,7 +1558,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>5.29962062835693</v>
+        <v>5.29962110519409</v>
       </c>
       <c r="H41" t="n">
         <v>390501</v>
@@ -1587,7 +1587,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>5.29962062835693</v>
+        <v>5.29962110519409</v>
       </c>
       <c r="H42" t="n">
         <v>506725</v>
@@ -1790,7 +1790,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G49" t="n">
-        <v>4.99917793273926</v>
+        <v>4.9991774559021</v>
       </c>
       <c r="H49" t="n">
         <v>389307</v>
@@ -1877,7 +1877,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G52" t="n">
-        <v>4.95485067367554</v>
+        <v>4.95485019683838</v>
       </c>
       <c r="H52" t="n">
         <v>406656</v>
@@ -2080,7 +2080,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G59" t="n">
-        <v>4.66918277740479</v>
+        <v>4.66918230056763</v>
       </c>
       <c r="H59" t="n">
         <v>322258</v>
@@ -2138,7 +2138,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G61" t="n">
-        <v>4.34608364105225</v>
+        <v>4.34608316421509</v>
       </c>
       <c r="H61" t="n">
         <v>512194</v>
@@ -2196,7 +2196,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G63" t="n">
-        <v>4.45838022232056</v>
+        <v>4.4583797454834</v>
       </c>
       <c r="H63" t="n">
         <v>651861</v>
@@ -2225,7 +2225,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G64" t="n">
-        <v>4.36381435394287</v>
+        <v>4.36381387710571</v>
       </c>
       <c r="H64" t="n">
         <v>521178</v>
@@ -2254,7 +2254,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>4.23575687408447</v>
+        <v>4.23575639724731</v>
       </c>
       <c r="H65" t="n">
         <v>607840</v>
@@ -2312,7 +2312,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G67" t="n">
-        <v>4.07420682907104</v>
+        <v>4.0742073059082</v>
       </c>
       <c r="H67" t="n">
         <v>347657</v>
@@ -2370,7 +2370,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.0584454536438</v>
+        <v>4.05844593048096</v>
       </c>
       <c r="H69" t="n">
         <v>275320</v>
@@ -2399,7 +2399,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.0879979133606</v>
+        <v>4.08799743652344</v>
       </c>
       <c r="H70" t="n">
         <v>183131</v>
@@ -2515,7 +2515,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>4.04859495162964</v>
+        <v>4.0485954284668</v>
       </c>
       <c r="H74" t="n">
         <v>139031</v>
@@ -2573,7 +2573,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G76" t="n">
-        <v>3.99343156814575</v>
+        <v>3.99343180656433</v>
       </c>
       <c r="H76" t="n">
         <v>239763</v>
@@ -2631,7 +2631,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G78" t="n">
-        <v>3.94220876693726</v>
+        <v>3.94220852851868</v>
       </c>
       <c r="H78" t="n">
         <v>199710</v>
@@ -2863,7 +2863,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G86" t="n">
-        <v>3.93629837036133</v>
+        <v>3.93629860877991</v>
       </c>
       <c r="H86" t="n">
         <v>139234</v>
@@ -2892,7 +2892,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G87" t="n">
-        <v>3.94417905807495</v>
+        <v>3.94417881965637</v>
       </c>
       <c r="H87" t="n">
         <v>95738</v>
@@ -3008,7 +3008,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95599913597107</v>
+        <v>3.95599937438965</v>
       </c>
       <c r="H91" t="n">
         <v>78796</v>
@@ -3037,7 +3037,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G92" t="n">
-        <v>3.92250752449036</v>
+        <v>3.92250776290894</v>
       </c>
       <c r="H92" t="n">
         <v>96082</v>
@@ -3153,7 +3153,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G96" t="n">
-        <v>3.93629837036133</v>
+        <v>3.93629860877991</v>
       </c>
       <c r="H96" t="n">
         <v>110034</v>
@@ -3211,7 +3211,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G98" t="n">
-        <v>3.91068696975708</v>
+        <v>3.9106867313385</v>
       </c>
       <c r="H98" t="n">
         <v>70667</v>
@@ -80183,6 +80183,35 @@
         <v>1101641</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>0.0229000002145767</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>0.0230000000447035</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>0.0211999993771315</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>0.0217000003904104</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>0.0217000003904104</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>987146</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MTV.MI.xlsx
+++ b/data/MTV.MI.xlsx
@@ -456,7 +456,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>5.74289798736572</v>
+        <v>5.74289751052856</v>
       </c>
       <c r="H3" t="n">
         <v>209257</v>
@@ -630,7 +630,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G9" t="n">
-        <v>5.71334600448608</v>
+        <v>5.71334648132324</v>
       </c>
       <c r="H9" t="n">
         <v>226982</v>
@@ -804,7 +804,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G15" t="n">
-        <v>4.90953731536865</v>
+        <v>4.90953779220581</v>
       </c>
       <c r="H15" t="n">
         <v>908989</v>
@@ -833,7 +833,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G16" t="n">
-        <v>5.16171264648438</v>
+        <v>5.16171216964722</v>
       </c>
       <c r="H16" t="n">
         <v>470293</v>
@@ -949,7 +949,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>5.21096515655518</v>
+        <v>5.21096563339233</v>
       </c>
       <c r="H20" t="n">
         <v>126286</v>
@@ -978,7 +978,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G21" t="n">
-        <v>5.17648887634277</v>
+        <v>5.17648839950562</v>
       </c>
       <c r="H21" t="n">
         <v>124704</v>
@@ -1007,7 +1007,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>5.21096515655518</v>
+        <v>5.21096563339233</v>
       </c>
       <c r="H22" t="n">
         <v>196742</v>
@@ -1181,7 +1181,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G28" t="n">
-        <v>3.58561730384827</v>
+        <v>3.58561706542969</v>
       </c>
       <c r="H28" t="n">
         <v>598311</v>
@@ -1239,7 +1239,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G30" t="n">
-        <v>3.79050946235657</v>
+        <v>3.79050970077515</v>
       </c>
       <c r="H30" t="n">
         <v>438905</v>
@@ -1268,7 +1268,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G31" t="n">
-        <v>3.90280628204346</v>
+        <v>3.90280604362488</v>
       </c>
       <c r="H31" t="n">
         <v>361003</v>
@@ -1355,7 +1355,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>4.62978029251099</v>
+        <v>4.62977981567383</v>
       </c>
       <c r="H34" t="n">
         <v>445139</v>
@@ -1384,7 +1384,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G35" t="n">
-        <v>4.57658720016479</v>
+        <v>4.57658672332764</v>
       </c>
       <c r="H35" t="n">
         <v>660456</v>
@@ -1471,7 +1471,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G38" t="n">
-        <v>5.51140880584717</v>
+        <v>5.51140832901001</v>
       </c>
       <c r="H38" t="n">
         <v>972499</v>
@@ -1558,7 +1558,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>5.29962110519409</v>
+        <v>5.29962062835693</v>
       </c>
       <c r="H41" t="n">
         <v>390501</v>
@@ -1587,7 +1587,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>5.29962110519409</v>
+        <v>5.29962062835693</v>
       </c>
       <c r="H42" t="n">
         <v>506725</v>
@@ -1790,7 +1790,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G49" t="n">
-        <v>4.9991774559021</v>
+        <v>4.99917793273926</v>
       </c>
       <c r="H49" t="n">
         <v>389307</v>
@@ -1877,7 +1877,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G52" t="n">
-        <v>4.95485019683838</v>
+        <v>4.95485067367554</v>
       </c>
       <c r="H52" t="n">
         <v>406656</v>
@@ -2080,7 +2080,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G59" t="n">
-        <v>4.66918230056763</v>
+        <v>4.66918277740479</v>
       </c>
       <c r="H59" t="n">
         <v>322258</v>
@@ -2138,7 +2138,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G61" t="n">
-        <v>4.34608316421509</v>
+        <v>4.34608364105225</v>
       </c>
       <c r="H61" t="n">
         <v>512194</v>
@@ -2196,7 +2196,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G63" t="n">
-        <v>4.4583797454834</v>
+        <v>4.45838022232056</v>
       </c>
       <c r="H63" t="n">
         <v>651861</v>
@@ -2225,7 +2225,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G64" t="n">
-        <v>4.36381387710571</v>
+        <v>4.36381435394287</v>
       </c>
       <c r="H64" t="n">
         <v>521178</v>
@@ -2254,7 +2254,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>4.23575639724731</v>
+        <v>4.23575687408447</v>
       </c>
       <c r="H65" t="n">
         <v>607840</v>
@@ -2312,7 +2312,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G67" t="n">
-        <v>4.0742073059082</v>
+        <v>4.07420682907104</v>
       </c>
       <c r="H67" t="n">
         <v>347657</v>
@@ -2370,7 +2370,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.05844593048096</v>
+        <v>4.0584454536438</v>
       </c>
       <c r="H69" t="n">
         <v>275320</v>
@@ -2399,7 +2399,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.08799743652344</v>
+        <v>4.0879979133606</v>
       </c>
       <c r="H70" t="n">
         <v>183131</v>
@@ -2515,7 +2515,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>4.0485954284668</v>
+        <v>4.04859495162964</v>
       </c>
       <c r="H74" t="n">
         <v>139031</v>
@@ -2573,7 +2573,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G76" t="n">
-        <v>3.99343180656433</v>
+        <v>3.99343156814575</v>
       </c>
       <c r="H76" t="n">
         <v>239763</v>
@@ -2631,7 +2631,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G78" t="n">
-        <v>3.94220852851868</v>
+        <v>3.94220876693726</v>
       </c>
       <c r="H78" t="n">
         <v>199710</v>
@@ -2863,7 +2863,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G86" t="n">
-        <v>3.93629860877991</v>
+        <v>3.93629837036133</v>
       </c>
       <c r="H86" t="n">
         <v>139234</v>
@@ -2892,7 +2892,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G87" t="n">
-        <v>3.94417881965637</v>
+        <v>3.94417905807495</v>
       </c>
       <c r="H87" t="n">
         <v>95738</v>
@@ -3008,7 +3008,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95599937438965</v>
+        <v>3.95599913597107</v>
       </c>
       <c r="H91" t="n">
         <v>78796</v>
@@ -3037,7 +3037,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G92" t="n">
-        <v>3.92250776290894</v>
+        <v>3.92250752449036</v>
       </c>
       <c r="H92" t="n">
         <v>96082</v>
@@ -3153,7 +3153,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G96" t="n">
-        <v>3.93629860877991</v>
+        <v>3.93629837036133</v>
       </c>
       <c r="H96" t="n">
         <v>110034</v>
@@ -3211,7 +3211,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G98" t="n">
-        <v>3.9106867313385</v>
+        <v>3.91068696975708</v>
       </c>
       <c r="H98" t="n">
         <v>70667</v>
@@ -80212,6 +80212,35 @@
         <v>987146</v>
       </c>
       <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>0.0209999997168779</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>0.0229000002145767</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>0.0209999997168779</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>0.0216000005602837</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>0.0216000005602837</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>342728</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
